--- a/photo_release_form_templates/026_employee_image_release_consent_form--photo_release_form_templates.xlsx
+++ b/photo_release_form_templates/026_employee_image_release_consent_form--photo_release_form_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -734,8 +734,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -763,12 +763,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'website_and_marketing_materials'}</t>
+          <t>website_and_marketing_materials</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Website and marketing materials'}</t>
+          <t>Website and marketing materials</t>
         </is>
       </c>
     </row>
@@ -780,12 +780,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'email_and_mail'}</t>
+          <t>email_and_mail</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Email and mail'}</t>
+          <t>Email and mail</t>
         </is>
       </c>
     </row>
@@ -797,12 +797,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'intranet_and_social_media'}</t>
+          <t>intranet_and_social_media</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Intranet and social media'}</t>
+          <t>Intranet and social media</t>
         </is>
       </c>
     </row>
@@ -814,12 +814,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'none_of_the_above'}</t>
+          <t>none_of_the_above</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'None of the above'}</t>
+          <t>None of the above</t>
         </is>
       </c>
     </row>
@@ -831,12 +831,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'to_use_my_name,_photo,_and_image'}</t>
+          <t>to_use_my_name,_photo,_and_image</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'to use my name, photo, and image'}</t>
+          <t>to use my name, photo, and image</t>
         </is>
       </c>
     </row>
@@ -848,12 +848,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'only_in_the_above_listed_options'}</t>
+          <t>only_in_the_above_listed_options</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'only in the above listed options'}</t>
+          <t>only in the above listed options</t>
         </is>
       </c>
     </row>
@@ -865,12 +865,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'neither_the_company_nor_i'}</t>
+          <t>neither_the_company_nor_i</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'neither the company nor I'}</t>
+          <t>neither the company nor I</t>
         </is>
       </c>
     </row>
